--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_R2.xlsx
@@ -451,49 +451,49 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4226732163016362</v>
+        <v>0.4226732165496458</v>
       </c>
       <c r="D2">
-        <v>0.6138839211684494</v>
+        <v>0.6138839210747038</v>
       </c>
       <c r="E2">
-        <v>0.6560003917844555</v>
+        <v>0.6560003917465025</v>
       </c>
       <c r="F2">
-        <v>0.6763348182047245</v>
+        <v>0.6763348180698748</v>
       </c>
       <c r="G2">
-        <v>0.7075797549612501</v>
+        <v>0.7075797549555246</v>
       </c>
       <c r="H2">
-        <v>0.7169462343775983</v>
+        <v>0.7169462340363307</v>
       </c>
       <c r="I2">
-        <v>0.736819128221714</v>
+        <v>0.7368191274659995</v>
       </c>
       <c r="J2">
-        <v>0.7562501938920931</v>
+        <v>0.7562501931513435</v>
       </c>
       <c r="K2">
-        <v>0.76129717022153</v>
+        <v>0.7612971694326165</v>
       </c>
       <c r="L2">
-        <v>0.7675591744150942</v>
+        <v>0.7675591736703034</v>
       </c>
       <c r="M2">
-        <v>0.7830358521120926</v>
+        <v>0.7830358509581677</v>
       </c>
       <c r="N2">
-        <v>0.7904921357124712</v>
+        <v>0.7904921346024287</v>
       </c>
       <c r="O2">
-        <v>0.8137724041543795</v>
+        <v>0.8137724051334142</v>
       </c>
       <c r="P2">
-        <v>0.830437527315436</v>
+        <v>0.8304375322839344</v>
       </c>
       <c r="Q2">
-        <v>0.8417037666528494</v>
+        <v>0.8417037713012822</v>
       </c>
     </row>
     <row r="3">
@@ -506,49 +506,49 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.5005860439610934</v>
+        <v>0.5005860390060386</v>
       </c>
       <c r="D3">
-        <v>0.6329577775013353</v>
+        <v>0.6329577775419658</v>
       </c>
       <c r="E3">
-        <v>0.6495964726922731</v>
+        <v>0.6495964732770507</v>
       </c>
       <c r="F3">
-        <v>0.6993756497156882</v>
+        <v>0.6993756488499419</v>
       </c>
       <c r="G3">
-        <v>0.7126751045868035</v>
+        <v>0.7126751050893465</v>
       </c>
       <c r="H3">
-        <v>0.7413693517109444</v>
+        <v>0.7413693552327163</v>
       </c>
       <c r="I3">
-        <v>0.7652751634870232</v>
+        <v>0.7652751710533382</v>
       </c>
       <c r="J3">
-        <v>0.7825354032661584</v>
+        <v>0.7825354157825678</v>
       </c>
       <c r="K3">
-        <v>0.801213664010606</v>
+        <v>0.8012136802931529</v>
       </c>
       <c r="L3">
-        <v>0.8170582807549697</v>
+        <v>0.817058301182893</v>
       </c>
       <c r="M3">
-        <v>0.8414621102586555</v>
+        <v>0.841462132457485</v>
       </c>
       <c r="N3">
-        <v>0.8532896308971735</v>
+        <v>0.8532896516445603</v>
       </c>
       <c r="O3">
-        <v>0.8773430706421189</v>
+        <v>0.8773430821949408</v>
       </c>
       <c r="P3">
-        <v>0.8890925322691144</v>
+        <v>0.8890925388358178</v>
       </c>
       <c r="Q3">
-        <v>0.9007527255040253</v>
+        <v>0.900752731983964</v>
       </c>
     </row>
     <row r="4">
@@ -561,49 +561,49 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.4435334755293588</v>
+        <v>0.4435334756459111</v>
       </c>
       <c r="D4">
-        <v>0.600791091792698</v>
+        <v>0.6007910916687293</v>
       </c>
       <c r="E4">
-        <v>0.6203175296441081</v>
+        <v>0.6203175296230591</v>
       </c>
       <c r="F4">
-        <v>0.6502090492697123</v>
+        <v>0.6502090492286721</v>
       </c>
       <c r="G4">
-        <v>0.6907959241636793</v>
+        <v>0.6907959227574074</v>
       </c>
       <c r="H4">
-        <v>0.7195321711578067</v>
+        <v>0.7195321697462357</v>
       </c>
       <c r="I4">
-        <v>0.732135750913034</v>
+        <v>0.7321357495885645</v>
       </c>
       <c r="J4">
-        <v>0.7466196098126303</v>
+        <v>0.7466196083368606</v>
       </c>
       <c r="K4">
-        <v>0.7705921354126433</v>
+        <v>0.770592133159886</v>
       </c>
       <c r="L4">
-        <v>0.7932698534804999</v>
+        <v>0.7932698515366601</v>
       </c>
       <c r="M4">
-        <v>0.8027958470869203</v>
+        <v>0.8027958461074555</v>
       </c>
       <c r="N4">
-        <v>0.8255327656170132</v>
+        <v>0.825532765737328</v>
       </c>
       <c r="O4">
-        <v>0.8393737670387228</v>
+        <v>0.8393737676170778</v>
       </c>
       <c r="P4">
-        <v>0.848089418138862</v>
+        <v>0.848089419665917</v>
       </c>
       <c r="Q4">
-        <v>0.8618835817022211</v>
+        <v>0.8618835844994979</v>
       </c>
     </row>
     <row r="5">
@@ -616,49 +616,49 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.6100318168402478</v>
+        <v>0.6100318170587467</v>
       </c>
       <c r="D5">
-        <v>0.6456035090591881</v>
+        <v>0.6456035093329955</v>
       </c>
       <c r="E5">
-        <v>0.6635752452708878</v>
+        <v>0.6635752454151093</v>
       </c>
       <c r="F5">
-        <v>0.6976069644309328</v>
+        <v>0.6976069645916962</v>
       </c>
       <c r="G5">
-        <v>0.7251106964022684</v>
+        <v>0.7251106978422603</v>
       </c>
       <c r="H5">
-        <v>0.7369106433437098</v>
+        <v>0.7369106441286662</v>
       </c>
       <c r="I5">
-        <v>0.7444859076384371</v>
+        <v>0.7444859085727902</v>
       </c>
       <c r="J5">
-        <v>0.7624378561161853</v>
+        <v>0.7624378556385814</v>
       </c>
       <c r="K5">
-        <v>0.78760020111444</v>
+        <v>0.7876002008508051</v>
       </c>
       <c r="L5">
-        <v>0.8059649867535625</v>
+        <v>0.8059649884975559</v>
       </c>
       <c r="M5">
-        <v>0.830366778796621</v>
+        <v>0.8303667791265055</v>
       </c>
       <c r="N5">
-        <v>0.8490138029684103</v>
+        <v>0.8490138058184866</v>
       </c>
       <c r="O5">
-        <v>0.8650169818653041</v>
+        <v>0.8650169849299519</v>
       </c>
       <c r="P5">
-        <v>0.8763531453168967</v>
+        <v>0.8763531500767945</v>
       </c>
       <c r="Q5">
-        <v>0.8882743931372074</v>
+        <v>0.8882743999407571</v>
       </c>
     </row>
     <row r="6">
@@ -671,49 +671,49 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.6070171617662247</v>
+        <v>0.6070171619989075</v>
       </c>
       <c r="D6">
-        <v>0.6393045257378471</v>
+        <v>0.6393045265012434</v>
       </c>
       <c r="E6">
-        <v>0.6610511929476248</v>
+        <v>0.6610511939442824</v>
       </c>
       <c r="F6">
-        <v>0.7001481256441999</v>
+        <v>0.7001481274750757</v>
       </c>
       <c r="G6">
-        <v>0.7246880100477294</v>
+        <v>0.72468801162317</v>
       </c>
       <c r="H6">
-        <v>0.7307487279863828</v>
+        <v>0.7307487295594213</v>
       </c>
       <c r="I6">
-        <v>0.749984657749466</v>
+        <v>0.7499846588558752</v>
       </c>
       <c r="J6">
-        <v>0.7661223764520513</v>
+        <v>0.7661223766813637</v>
       </c>
       <c r="K6">
-        <v>0.780111668543195</v>
+        <v>0.7801116699312639</v>
       </c>
       <c r="L6">
-        <v>0.7929170623352036</v>
+        <v>0.7929170652407993</v>
       </c>
       <c r="M6">
-        <v>0.8099297843089326</v>
+        <v>0.8099297896289367</v>
       </c>
       <c r="N6">
-        <v>0.8274049901785364</v>
+        <v>0.8274049991033307</v>
       </c>
       <c r="O6">
-        <v>0.8482249877342345</v>
+        <v>0.8482250004940552</v>
       </c>
       <c r="P6">
-        <v>0.8595225665143156</v>
+        <v>0.8595225807498292</v>
       </c>
       <c r="Q6">
-        <v>0.8731733790000817</v>
+        <v>0.8731733920375879</v>
       </c>
     </row>
     <row r="7">
@@ -726,49 +726,49 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.4485490768089913</v>
+        <v>0.4485490769484015</v>
       </c>
       <c r="D7">
-        <v>0.61201724408647</v>
+        <v>0.6120172439931942</v>
       </c>
       <c r="E7">
-        <v>0.676416279468887</v>
+        <v>0.6764162792676429</v>
       </c>
       <c r="F7">
-        <v>0.6880526294465205</v>
+        <v>0.6880526294662277</v>
       </c>
       <c r="G7">
-        <v>0.7135555272214058</v>
+        <v>0.7135555270394232</v>
       </c>
       <c r="H7">
-        <v>0.7202028579663428</v>
+        <v>0.7202028573689703</v>
       </c>
       <c r="I7">
-        <v>0.7360009114323256</v>
+        <v>0.7360009103708571</v>
       </c>
       <c r="J7">
-        <v>0.753229656421244</v>
+        <v>0.7532296554488426</v>
       </c>
       <c r="K7">
-        <v>0.7705416090376991</v>
+        <v>0.7705416083314932</v>
       </c>
       <c r="L7">
-        <v>0.783722773582618</v>
+        <v>0.783722771844954</v>
       </c>
       <c r="M7">
-        <v>0.8042615261658581</v>
+        <v>0.8042615248751608</v>
       </c>
       <c r="N7">
-        <v>0.8234075120408724</v>
+        <v>0.8234075161540007</v>
       </c>
       <c r="O7">
-        <v>0.8352283264744101</v>
+        <v>0.8352283296722679</v>
       </c>
       <c r="P7">
-        <v>0.8483520578819547</v>
+        <v>0.8483520631449875</v>
       </c>
       <c r="Q7">
-        <v>0.8581856967680425</v>
+        <v>0.8581857061046585</v>
       </c>
     </row>
     <row r="8">
@@ -781,49 +781,49 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.5206052769768158</v>
+        <v>0.5206052768054965</v>
       </c>
       <c r="D8">
-        <v>0.6078732584528704</v>
+        <v>0.6078732582975199</v>
       </c>
       <c r="E8">
-        <v>0.6768386823180945</v>
+        <v>0.6768386826477882</v>
       </c>
       <c r="F8">
-        <v>0.7037229690604321</v>
+        <v>0.7037229692087383</v>
       </c>
       <c r="G8">
-        <v>0.7121855486138966</v>
+        <v>0.712185548317009</v>
       </c>
       <c r="H8">
-        <v>0.7348135597008684</v>
+        <v>0.734813558818933</v>
       </c>
       <c r="I8">
-        <v>0.7427445006452336</v>
+        <v>0.7427444995171902</v>
       </c>
       <c r="J8">
-        <v>0.7597145142683589</v>
+        <v>0.7597145118491005</v>
       </c>
       <c r="K8">
-        <v>0.7746048816464201</v>
+        <v>0.774604877817791</v>
       </c>
       <c r="L8">
-        <v>0.789588720110749</v>
+        <v>0.7895887154589716</v>
       </c>
       <c r="M8">
-        <v>0.8031058147400687</v>
+        <v>0.8031058128841662</v>
       </c>
       <c r="N8">
-        <v>0.816693849482493</v>
+        <v>0.8166938500560126</v>
       </c>
       <c r="O8">
-        <v>0.8268848490434663</v>
+        <v>0.8268848499637843</v>
       </c>
       <c r="P8">
-        <v>0.8435914127577882</v>
+        <v>0.8435914139994118</v>
       </c>
       <c r="Q8">
-        <v>0.8577375082572827</v>
+        <v>0.8577375092894336</v>
       </c>
     </row>
     <row r="9">
@@ -836,49 +836,49 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.5205623175890227</v>
+        <v>0.5205623174173816</v>
       </c>
       <c r="D9">
-        <v>0.60784629969889</v>
+        <v>0.6078462995421252</v>
       </c>
       <c r="E9">
-        <v>0.6766332412951904</v>
+        <v>0.6766332416224113</v>
       </c>
       <c r="F9">
-        <v>0.7028171165111605</v>
+        <v>0.7028171166575812</v>
       </c>
       <c r="G9">
-        <v>0.7100060660481193</v>
+        <v>0.7100060657366675</v>
       </c>
       <c r="H9">
-        <v>0.7286237616018298</v>
+        <v>0.7286237605591488</v>
       </c>
       <c r="I9">
-        <v>0.734203989890325</v>
+        <v>0.7342039886324163</v>
       </c>
       <c r="J9">
-        <v>0.7416622158583425</v>
+        <v>0.7416622133417443</v>
       </c>
       <c r="K9">
-        <v>0.7462717478579692</v>
+        <v>0.7462717439651957</v>
       </c>
       <c r="L9">
-        <v>0.7541234170239347</v>
+        <v>0.7541234105135952</v>
       </c>
       <c r="M9">
-        <v>0.7585244018577597</v>
+        <v>0.7585243951298893</v>
       </c>
       <c r="N9">
-        <v>0.7646851494990351</v>
+        <v>0.7646851437894226</v>
       </c>
       <c r="O9">
-        <v>0.7689951138495983</v>
+        <v>0.768995108833338</v>
       </c>
       <c r="P9">
-        <v>0.7761696970643259</v>
+        <v>0.7761696929858984</v>
       </c>
       <c r="Q9">
-        <v>0.7800405819156587</v>
+        <v>0.7800405786905309</v>
       </c>
     </row>
     <row r="10">
@@ -891,49 +891,49 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.5205230327394337</v>
+        <v>0.5205230325672237</v>
       </c>
       <c r="D10">
-        <v>0.6078334575093147</v>
+        <v>0.6078334573523654</v>
       </c>
       <c r="E10">
-        <v>0.6765871964360762</v>
+        <v>0.6765871967603111</v>
       </c>
       <c r="F10">
-        <v>0.7027455658396173</v>
+        <v>0.7027455659850992</v>
       </c>
       <c r="G10">
-        <v>0.7099420570343165</v>
+        <v>0.7099420567253972</v>
       </c>
       <c r="H10">
-        <v>0.7284543386780953</v>
+        <v>0.7284543376309593</v>
       </c>
       <c r="I10">
-        <v>0.7338969276303087</v>
+        <v>0.7338969263742887</v>
       </c>
       <c r="J10">
-        <v>0.7410681466041162</v>
+        <v>0.7410681441106833</v>
       </c>
       <c r="K10">
-        <v>0.745385805177039</v>
+        <v>0.7453858013393864</v>
       </c>
       <c r="L10">
-        <v>0.7525764391054717</v>
+        <v>0.7525764326607678</v>
       </c>
       <c r="M10">
-        <v>0.7564737602597286</v>
+        <v>0.7564737534581263</v>
       </c>
       <c r="N10">
-        <v>0.7616680137893131</v>
+        <v>0.761668007630717</v>
       </c>
       <c r="O10">
-        <v>0.7655557673130832</v>
+        <v>0.765555761681513</v>
       </c>
       <c r="P10">
-        <v>0.772519523027285</v>
+        <v>0.7725195181219768</v>
       </c>
       <c r="Q10">
-        <v>0.7766760465580256</v>
+        <v>0.7766760425429213</v>
       </c>
     </row>
     <row r="11">
@@ -946,49 +946,49 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.5205642637601677</v>
+        <v>0.5205642635882819</v>
       </c>
       <c r="D11">
-        <v>0.6078198436452922</v>
+        <v>0.6078198434884154</v>
       </c>
       <c r="E11">
-        <v>0.6764687298641887</v>
+        <v>0.6764687301949653</v>
       </c>
       <c r="F11">
-        <v>0.7026497284810076</v>
+        <v>0.7026497286332243</v>
       </c>
       <c r="G11">
-        <v>0.7099242198630991</v>
+        <v>0.7099242195641284</v>
       </c>
       <c r="H11">
-        <v>0.7288095526977996</v>
+        <v>0.7288095516452373</v>
       </c>
       <c r="I11">
-        <v>0.7351042901912949</v>
+        <v>0.7351042888802444</v>
       </c>
       <c r="J11">
-        <v>0.7448741713625877</v>
+        <v>0.7448741686629163</v>
       </c>
       <c r="K11">
-        <v>0.7510992033293369</v>
+        <v>0.7510991991056868</v>
       </c>
       <c r="L11">
-        <v>0.7589391668194596</v>
+        <v>0.758939160456013</v>
       </c>
       <c r="M11">
-        <v>0.7632262826815993</v>
+        <v>0.7632262761089041</v>
       </c>
       <c r="N11">
-        <v>0.7686588052349057</v>
+        <v>0.7686587994525806</v>
       </c>
       <c r="O11">
-        <v>0.7718341747693007</v>
+        <v>0.771834169706343</v>
       </c>
       <c r="P11">
-        <v>0.7779698825016332</v>
+        <v>0.7779698787547843</v>
       </c>
       <c r="Q11">
-        <v>0.7807528906390273</v>
+        <v>0.7807528866368051</v>
       </c>
     </row>
     <row r="12">
@@ -1001,49 +1001,49 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0.6256684992605344</v>
+        <v>0.6256684995277224</v>
       </c>
       <c r="D12">
-        <v>0.6630786191967493</v>
+        <v>0.6630786196249348</v>
       </c>
       <c r="E12">
-        <v>0.6819965972183346</v>
+        <v>0.6819965975466808</v>
       </c>
       <c r="F12">
-        <v>0.7147027132907793</v>
+        <v>0.7147027138091129</v>
       </c>
       <c r="G12">
-        <v>0.7362379508688577</v>
+        <v>0.7362379522115026</v>
       </c>
       <c r="H12">
-        <v>0.7469515443669583</v>
+        <v>0.7469515456445683</v>
       </c>
       <c r="I12">
-        <v>0.7565681659873583</v>
+        <v>0.7565681673485567</v>
       </c>
       <c r="J12">
-        <v>0.7683866818759123</v>
+        <v>0.7683866825986925</v>
       </c>
       <c r="K12">
-        <v>0.7841498226811183</v>
+        <v>0.7841498234934453</v>
       </c>
       <c r="L12">
-        <v>0.8009544486888206</v>
+        <v>0.8009544512679112</v>
       </c>
       <c r="M12">
-        <v>0.8268471550639334</v>
+        <v>0.8268471557197383</v>
       </c>
       <c r="N12">
-        <v>0.8406186594429166</v>
+        <v>0.8406186601867291</v>
       </c>
       <c r="O12">
-        <v>0.8534902639285242</v>
+        <v>0.8534902624007316</v>
       </c>
       <c r="P12">
-        <v>0.8644780794675748</v>
+        <v>0.8644780766836552</v>
       </c>
       <c r="Q12">
-        <v>0.8749142902315558</v>
+        <v>0.8749142852881248</v>
       </c>
     </row>
     <row r="13">
@@ -1056,49 +1056,49 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0.623600934933505</v>
+        <v>0.6236009350049492</v>
       </c>
       <c r="D13">
-        <v>0.6724030165401826</v>
+        <v>0.6724030166463889</v>
       </c>
       <c r="E13">
-        <v>0.7048940196226932</v>
+        <v>0.7048940195481492</v>
       </c>
       <c r="F13">
-        <v>0.7262105491165037</v>
+        <v>0.7262105515173098</v>
       </c>
       <c r="G13">
-        <v>0.7383713157551386</v>
+        <v>0.738371318809367</v>
       </c>
       <c r="H13">
-        <v>0.7631285723867025</v>
+        <v>0.7631285737498877</v>
       </c>
       <c r="I13">
-        <v>0.7768540342483207</v>
+        <v>0.7768540359774523</v>
       </c>
       <c r="J13">
-        <v>0.7916642318861681</v>
+        <v>0.7916642338696807</v>
       </c>
       <c r="K13">
-        <v>0.8111424369511484</v>
+        <v>0.8111424365140055</v>
       </c>
       <c r="L13">
-        <v>0.8292586947578544</v>
+        <v>0.8292586980788871</v>
       </c>
       <c r="M13">
-        <v>0.838455531982401</v>
+        <v>0.8384555379789667</v>
       </c>
       <c r="N13">
-        <v>0.8476495289339984</v>
+        <v>0.8476495395506208</v>
       </c>
       <c r="O13">
-        <v>0.8552980048096673</v>
+        <v>0.8552980134334724</v>
       </c>
       <c r="P13">
-        <v>0.8636449591608242</v>
+        <v>0.8636449676929638</v>
       </c>
       <c r="Q13">
-        <v>0.8705691232402755</v>
+        <v>0.8705691329727364</v>
       </c>
     </row>
     <row r="14">
@@ -1111,49 +1111,49 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>0.4485398169543739</v>
+        <v>0.4485398170934217</v>
       </c>
       <c r="D14">
-        <v>0.6120047585857009</v>
+        <v>0.6120047584910573</v>
       </c>
       <c r="E14">
-        <v>0.6763062763003131</v>
+        <v>0.6763062760980596</v>
       </c>
       <c r="F14">
-        <v>0.6878703626195042</v>
+        <v>0.6878703626393846</v>
       </c>
       <c r="G14">
-        <v>0.7128328963973657</v>
+        <v>0.7128328962262438</v>
       </c>
       <c r="H14">
-        <v>0.7188079138014601</v>
+        <v>0.7188079132259079</v>
       </c>
       <c r="I14">
-        <v>0.7321503554785089</v>
+        <v>0.7321503543348931</v>
       </c>
       <c r="J14">
-        <v>0.7464360105776009</v>
+        <v>0.7464360093096869</v>
       </c>
       <c r="K14">
-        <v>0.7575777158710986</v>
+        <v>0.757577714681643</v>
       </c>
       <c r="L14">
-        <v>0.7655713227924297</v>
+        <v>0.7655713206250591</v>
       </c>
       <c r="M14">
-        <v>0.7732484260914736</v>
+        <v>0.7732484233298798</v>
       </c>
       <c r="N14">
-        <v>0.7773295341039215</v>
+        <v>0.7773295323796515</v>
       </c>
       <c r="O14">
-        <v>0.7824535508271264</v>
+        <v>0.7824535513957942</v>
       </c>
       <c r="P14">
-        <v>0.7870817943225555</v>
+        <v>0.7870817985588006</v>
       </c>
       <c r="Q14">
-        <v>0.7927494725763725</v>
+        <v>0.7927494791658134</v>
       </c>
     </row>
     <row r="15">
@@ -1166,49 +1166,49 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0.448511715328396</v>
+        <v>0.4485117154680227</v>
       </c>
       <c r="D15">
-        <v>0.6120032947009737</v>
+        <v>0.6120032946067177</v>
       </c>
       <c r="E15">
-        <v>0.6762586925598717</v>
+        <v>0.6762586923585296</v>
       </c>
       <c r="F15">
-        <v>0.6878087637275889</v>
+        <v>0.687808763748508</v>
       </c>
       <c r="G15">
-        <v>0.712700239775986</v>
+        <v>0.7127002396053117</v>
       </c>
       <c r="H15">
-        <v>0.7185632200713277</v>
+        <v>0.7185632195033188</v>
       </c>
       <c r="I15">
-        <v>0.7313985817540859</v>
+        <v>0.7313985806369288</v>
       </c>
       <c r="J15">
-        <v>0.7451195419212586</v>
+        <v>0.7451195407151904</v>
       </c>
       <c r="K15">
-        <v>0.7551617992987796</v>
+        <v>0.7551617982218479</v>
       </c>
       <c r="L15">
-        <v>0.7623327996823989</v>
+        <v>0.7623327978307617</v>
       </c>
       <c r="M15">
-        <v>0.768741351489313</v>
+        <v>0.7687413491641231</v>
       </c>
       <c r="N15">
-        <v>0.7727528621171182</v>
+        <v>0.772752860381046</v>
       </c>
       <c r="O15">
-        <v>0.7791242477083333</v>
+        <v>0.7791242478563758</v>
       </c>
       <c r="P15">
-        <v>0.783352542439949</v>
+        <v>0.7833525457493197</v>
       </c>
       <c r="Q15">
-        <v>0.7860256116781796</v>
+        <v>0.7860256165075203</v>
       </c>
     </row>
     <row r="16">
@@ -1221,49 +1221,49 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0.448476346110824</v>
+        <v>0.4484763462500794</v>
       </c>
       <c r="D16">
-        <v>0.6119996016794711</v>
+        <v>0.6119996015841751</v>
       </c>
       <c r="E16">
-        <v>0.6761995977983097</v>
+        <v>0.6761995975958544</v>
       </c>
       <c r="F16">
-        <v>0.6877566283887291</v>
+        <v>0.6877566284081869</v>
       </c>
       <c r="G16">
-        <v>0.7126973949292821</v>
+        <v>0.71269739476026</v>
       </c>
       <c r="H16">
-        <v>0.7185199001842656</v>
+        <v>0.7185198996171657</v>
       </c>
       <c r="I16">
-        <v>0.7310524955354933</v>
+        <v>0.7310524944190255</v>
       </c>
       <c r="J16">
-        <v>0.7442990558997337</v>
+        <v>0.7442990546667488</v>
       </c>
       <c r="K16">
-        <v>0.7534807251128877</v>
+        <v>0.7534807239877417</v>
       </c>
       <c r="L16">
-        <v>0.760408363610112</v>
+        <v>0.7604083617425883</v>
       </c>
       <c r="M16">
-        <v>0.765723677635098</v>
+        <v>0.765723675276799</v>
       </c>
       <c r="N16">
-        <v>0.770422751839026</v>
+        <v>0.7704227502643802</v>
       </c>
       <c r="O16">
-        <v>0.7763525053617326</v>
+        <v>0.7763525055791093</v>
       </c>
       <c r="P16">
-        <v>0.7821635191024041</v>
+        <v>0.7821635236213812</v>
       </c>
       <c r="Q16">
-        <v>0.7850589466587238</v>
+        <v>0.7850589524700946</v>
       </c>
     </row>
     <row r="17">
@@ -1276,49 +1276,49 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0.4483883977671762</v>
+        <v>0.4483883979054948</v>
       </c>
       <c r="D17">
-        <v>0.6119913577504019</v>
+        <v>0.6119913576537817</v>
       </c>
       <c r="E17">
-        <v>0.6760864073434152</v>
+        <v>0.6760864071390248</v>
       </c>
       <c r="F17">
-        <v>0.6876694066214953</v>
+        <v>0.6876694066381064</v>
       </c>
       <c r="G17">
-        <v>0.7127258522238242</v>
+        <v>0.7127258520534295</v>
       </c>
       <c r="H17">
-        <v>0.7185493417264381</v>
+        <v>0.7185493411531061</v>
       </c>
       <c r="I17">
-        <v>0.7308744008531578</v>
+        <v>0.730874399733848</v>
       </c>
       <c r="J17">
-        <v>0.7440946090728079</v>
+        <v>0.7440946078391201</v>
       </c>
       <c r="K17">
-        <v>0.7525416934845811</v>
+        <v>0.7525416923556033</v>
       </c>
       <c r="L17">
-        <v>0.7596468122731121</v>
+        <v>0.7596468104820376</v>
       </c>
       <c r="M17">
-        <v>0.7642136766817194</v>
+        <v>0.764213674451597</v>
       </c>
       <c r="N17">
-        <v>0.7689700890305078</v>
+        <v>0.7689700879393518</v>
       </c>
       <c r="O17">
-        <v>0.7735409597238408</v>
+        <v>0.7735409609506416</v>
       </c>
       <c r="P17">
-        <v>0.7790692820746439</v>
+        <v>0.7790692874181352</v>
       </c>
       <c r="Q17">
-        <v>0.7817854829898545</v>
+        <v>0.7817854900815581</v>
       </c>
     </row>
     <row r="18">
@@ -1331,49 +1331,49 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0.6254383605318308</v>
+        <v>0.6254383607921536</v>
       </c>
       <c r="D18">
-        <v>0.6615932431008031</v>
+        <v>0.6615932435039857</v>
       </c>
       <c r="E18">
-        <v>0.6803159302351702</v>
+        <v>0.6803159305241049</v>
       </c>
       <c r="F18">
-        <v>0.7141598823445331</v>
+        <v>0.7141598827666347</v>
       </c>
       <c r="G18">
-        <v>0.7359262614007329</v>
+        <v>0.7359262627309882</v>
       </c>
       <c r="H18">
-        <v>0.7490036951458934</v>
+        <v>0.7490036965056753</v>
       </c>
       <c r="I18">
-        <v>0.7548996462337879</v>
+        <v>0.7548996475605068</v>
       </c>
       <c r="J18">
-        <v>0.7687696820856427</v>
+        <v>0.7687696827271002</v>
       </c>
       <c r="K18">
-        <v>0.7851600933200761</v>
+        <v>0.785160093807154</v>
       </c>
       <c r="L18">
-        <v>0.8065791099999177</v>
+        <v>0.8065791129326897</v>
       </c>
       <c r="M18">
-        <v>0.8337853679740084</v>
+        <v>0.8337853709063427</v>
       </c>
       <c r="N18">
-        <v>0.8537398902986324</v>
+        <v>0.8537398959053895</v>
       </c>
       <c r="O18">
-        <v>0.8695941886802027</v>
+        <v>0.8695941941724757</v>
       </c>
       <c r="P18">
-        <v>0.8802843150270426</v>
+        <v>0.8802843220730754</v>
       </c>
       <c r="Q18">
-        <v>0.8906915769326352</v>
+        <v>0.8906915856461557</v>
       </c>
     </row>
     <row r="19">
@@ -1386,49 +1386,49 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0.6224919371108901</v>
+        <v>0.6224919373947508</v>
       </c>
       <c r="D19">
-        <v>0.6569526195550701</v>
+        <v>0.6569526205101114</v>
       </c>
       <c r="E19">
-        <v>0.6800145127323822</v>
+        <v>0.6800145138052947</v>
       </c>
       <c r="F19">
-        <v>0.7165034068000445</v>
+        <v>0.7165034082796765</v>
       </c>
       <c r="G19">
-        <v>0.7328083539668219</v>
+        <v>0.7328083555274494</v>
       </c>
       <c r="H19">
-        <v>0.7496493698460083</v>
+        <v>0.7496493723881221</v>
       </c>
       <c r="I19">
-        <v>0.7537754773242387</v>
+        <v>0.7537754793563489</v>
       </c>
       <c r="J19">
-        <v>0.7681085013189776</v>
+        <v>0.7681085036352001</v>
       </c>
       <c r="K19">
-        <v>0.7814253983096977</v>
+        <v>0.7814254014204703</v>
       </c>
       <c r="L19">
-        <v>0.7960308910790488</v>
+        <v>0.7960308973195072</v>
       </c>
       <c r="M19">
-        <v>0.8111325045249616</v>
+        <v>0.8111325128062459</v>
       </c>
       <c r="N19">
-        <v>0.8255041231691379</v>
+        <v>0.825504135421071</v>
       </c>
       <c r="O19">
-        <v>0.8464922887994928</v>
+        <v>0.8464923064611596</v>
       </c>
       <c r="P19">
-        <v>0.8601290595470664</v>
+        <v>0.8601290798431303</v>
       </c>
       <c r="Q19">
-        <v>0.8763064415308368</v>
+        <v>0.8763064613178148</v>
       </c>
     </row>
     <row r="20">
@@ -1441,49 +1441,49 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0.6210910742831441</v>
+        <v>0.6210910744724669</v>
       </c>
       <c r="D20">
-        <v>0.652308683871048</v>
+        <v>0.6523086847929229</v>
       </c>
       <c r="E20">
-        <v>0.6890106574368681</v>
+        <v>0.6890106585289716</v>
       </c>
       <c r="F20">
-        <v>0.7201519444868552</v>
+        <v>0.7201519454943919</v>
       </c>
       <c r="G20">
-        <v>0.7271502225270039</v>
+        <v>0.7271502235733336</v>
       </c>
       <c r="H20">
-        <v>0.7365979628652959</v>
+        <v>0.7365979630255401</v>
       </c>
       <c r="I20">
-        <v>0.7417708681833041</v>
+        <v>0.7417708682939842</v>
       </c>
       <c r="J20">
-        <v>0.7585368445752898</v>
+        <v>0.7585368442245055</v>
       </c>
       <c r="K20">
-        <v>0.7672528962768913</v>
+        <v>0.7672528959920923</v>
       </c>
       <c r="L20">
-        <v>0.7804805812174564</v>
+        <v>0.7804805828666369</v>
       </c>
       <c r="M20">
-        <v>0.7933934279889968</v>
+        <v>0.793393432740533</v>
       </c>
       <c r="N20">
-        <v>0.8052069952171826</v>
+        <v>0.8052070049323004</v>
       </c>
       <c r="O20">
-        <v>0.8128029480333711</v>
+        <v>0.8128029607183663</v>
       </c>
       <c r="P20">
-        <v>0.8252811874362772</v>
+        <v>0.8252812046124661</v>
       </c>
       <c r="Q20">
-        <v>0.8408514889068348</v>
+        <v>0.8408515097192512</v>
       </c>
     </row>
     <row r="21">
@@ -1496,49 +1496,49 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0.4998168181581377</v>
+        <v>0.4998168131317556</v>
       </c>
       <c r="D21">
-        <v>0.6309499478194083</v>
+        <v>0.6309499477565452</v>
       </c>
       <c r="E21">
-        <v>0.6473903684835799</v>
+        <v>0.6473903688093816</v>
       </c>
       <c r="F21">
-        <v>0.7024265058158221</v>
+        <v>0.7024265033399304</v>
       </c>
       <c r="G21">
-        <v>0.712791072219251</v>
+        <v>0.7127910714888923</v>
       </c>
       <c r="H21">
-        <v>0.729866326392413</v>
+        <v>0.729866325147372</v>
       </c>
       <c r="I21">
-        <v>0.7532352813101333</v>
+        <v>0.7532352815743071</v>
       </c>
       <c r="J21">
-        <v>0.7806191687085745</v>
+        <v>0.7806191704272818</v>
       </c>
       <c r="K21">
-        <v>0.7994655046766843</v>
+        <v>0.7994655118822841</v>
       </c>
       <c r="L21">
-        <v>0.8225420820690176</v>
+        <v>0.8225420957461171</v>
       </c>
       <c r="M21">
-        <v>0.8438822741112624</v>
+        <v>0.8438822866260492</v>
       </c>
       <c r="N21">
-        <v>0.8584961400551591</v>
+        <v>0.8584961460922937</v>
       </c>
       <c r="O21">
-        <v>0.8809394737254775</v>
+        <v>0.8809394755801971</v>
       </c>
       <c r="P21">
-        <v>0.8908000221854809</v>
+        <v>0.8908000184569481</v>
       </c>
       <c r="Q21">
-        <v>0.9011362193708056</v>
+        <v>0.9011362186316173</v>
       </c>
     </row>
     <row r="22">
@@ -1551,49 +1551,49 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0.4985239285187345</v>
+        <v>0.4985239234639995</v>
       </c>
       <c r="D22">
-        <v>0.6304023384182063</v>
+        <v>0.6304023383533806</v>
       </c>
       <c r="E22">
-        <v>0.6456991833217144</v>
+        <v>0.6456991835551377</v>
       </c>
       <c r="F22">
-        <v>0.7036636498679292</v>
+        <v>0.7036636470613336</v>
       </c>
       <c r="G22">
-        <v>0.7159647422967884</v>
+        <v>0.7159647419985862</v>
       </c>
       <c r="H22">
-        <v>0.7283842663457809</v>
+        <v>0.7283842674024126</v>
       </c>
       <c r="I22">
-        <v>0.7572032707875759</v>
+        <v>0.7572032751311787</v>
       </c>
       <c r="J22">
-        <v>0.7742680749506569</v>
+        <v>0.7742680820437958</v>
       </c>
       <c r="K22">
-        <v>0.8005978862523466</v>
+        <v>0.8005979043706564</v>
       </c>
       <c r="L22">
-        <v>0.8249564073981428</v>
+        <v>0.8249564347533315</v>
       </c>
       <c r="M22">
-        <v>0.8477920301836672</v>
+        <v>0.847792059529779</v>
       </c>
       <c r="N22">
-        <v>0.8760459809096657</v>
+        <v>0.8760460070707023</v>
       </c>
       <c r="O22">
-        <v>0.8865231969815063</v>
+        <v>0.8865232176191793</v>
       </c>
       <c r="P22">
-        <v>0.8941932170273209</v>
+        <v>0.8941932349051586</v>
       </c>
       <c r="Q22">
-        <v>0.9039007781150128</v>
+        <v>0.9039007926455856</v>
       </c>
     </row>
     <row r="23">
@@ -1606,49 +1606,49 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>0.6203813130959508</v>
+        <v>0.6203813126714877</v>
       </c>
       <c r="D23">
-        <v>0.6311306728877625</v>
+        <v>0.6311306725670776</v>
       </c>
       <c r="E23">
-        <v>0.6684970969902839</v>
+        <v>0.6684970991238876</v>
       </c>
       <c r="F23">
-        <v>0.6722097472374784</v>
+        <v>0.6722097484262515</v>
       </c>
       <c r="G23">
-        <v>0.7017561025895327</v>
+        <v>0.701756098617776</v>
       </c>
       <c r="H23">
-        <v>0.7431719140563344</v>
+        <v>0.7431718975152655</v>
       </c>
       <c r="I23">
-        <v>0.7714812935442726</v>
+        <v>0.7714812670421631</v>
       </c>
       <c r="J23">
-        <v>0.7921852391362674</v>
+        <v>0.7921852126728467</v>
       </c>
       <c r="K23">
-        <v>0.815613428682767</v>
+        <v>0.8156133804286628</v>
       </c>
       <c r="L23">
-        <v>0.842783184662832</v>
+        <v>0.8427831095245482</v>
       </c>
       <c r="M23">
-        <v>0.8673403315813437</v>
+        <v>0.8673402571454644</v>
       </c>
       <c r="N23">
-        <v>0.8845524947129213</v>
+        <v>0.8845524261151968</v>
       </c>
       <c r="O23">
-        <v>0.89876866316934</v>
+        <v>0.8987685952355365</v>
       </c>
       <c r="P23">
-        <v>0.9076164970125759</v>
+        <v>0.9076164382615417</v>
       </c>
       <c r="Q23">
-        <v>0.9213825246937632</v>
+        <v>0.9213824780548048</v>
       </c>
     </row>
     <row r="24">
@@ -1661,49 +1661,49 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0.614293658835778</v>
+        <v>0.6142936588429682</v>
       </c>
       <c r="D24">
-        <v>0.6579530093224538</v>
+        <v>0.6579530092539756</v>
       </c>
       <c r="E24">
-        <v>0.6786271129734901</v>
+        <v>0.6786271126509198</v>
       </c>
       <c r="F24">
-        <v>0.6848071581086843</v>
+        <v>0.6848071578053214</v>
       </c>
       <c r="G24">
-        <v>0.6959954095143736</v>
+        <v>0.6959954086694966</v>
       </c>
       <c r="H24">
-        <v>0.7129194161128041</v>
+        <v>0.7129194143049866</v>
       </c>
       <c r="I24">
-        <v>0.7221748618644271</v>
+        <v>0.7221748605540443</v>
       </c>
       <c r="J24">
-        <v>0.7783328774450973</v>
+        <v>0.7783328814092324</v>
       </c>
       <c r="K24">
-        <v>0.8127068975113949</v>
+        <v>0.8127069100834183</v>
       </c>
       <c r="L24">
-        <v>0.8383391899263134</v>
+        <v>0.838339207036938</v>
       </c>
       <c r="M24">
-        <v>0.8636918438811174</v>
+        <v>0.8636918676412975</v>
       </c>
       <c r="N24">
-        <v>0.8915462502703473</v>
+        <v>0.8915462736969275</v>
       </c>
       <c r="O24">
-        <v>0.9021152091386175</v>
+        <v>0.9021152315276106</v>
       </c>
       <c r="P24">
-        <v>0.9152495330703383</v>
+        <v>0.9152495469616676</v>
       </c>
       <c r="Q24">
-        <v>0.928462629866889</v>
+        <v>0.9284626377002055</v>
       </c>
     </row>
     <row r="25">
@@ -1716,49 +1716,49 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0.6181119563074844</v>
+        <v>0.6181119563178272</v>
       </c>
       <c r="D25">
-        <v>0.6612598818690909</v>
+        <v>0.6612598818016115</v>
       </c>
       <c r="E25">
-        <v>0.6845441378969188</v>
+        <v>0.6845441376268329</v>
       </c>
       <c r="F25">
-        <v>0.689906399203346</v>
+        <v>0.6899063989589901</v>
       </c>
       <c r="G25">
-        <v>0.6985594922472322</v>
+        <v>0.6985594915420643</v>
       </c>
       <c r="H25">
-        <v>0.7176185594169233</v>
+        <v>0.7176185583662016</v>
       </c>
       <c r="I25">
-        <v>0.7251891423444052</v>
+        <v>0.7251891415379905</v>
       </c>
       <c r="J25">
-        <v>0.7836483357880547</v>
+        <v>0.7836483413555221</v>
       </c>
       <c r="K25">
-        <v>0.7971968629236641</v>
+        <v>0.7971968713790782</v>
       </c>
       <c r="L25">
-        <v>0.8286904476556984</v>
+        <v>0.8286904664392614</v>
       </c>
       <c r="M25">
-        <v>0.8467960573097729</v>
+        <v>0.8467960777004282</v>
       </c>
       <c r="N25">
-        <v>0.8754871832530274</v>
+        <v>0.8754872121112122</v>
       </c>
       <c r="O25">
-        <v>0.8975799559938856</v>
+        <v>0.8975799831435368</v>
       </c>
       <c r="P25">
-        <v>0.9053066278574506</v>
+        <v>0.9053066518786463</v>
       </c>
       <c r="Q25">
-        <v>0.9201168820736503</v>
+        <v>0.9201168967531077</v>
       </c>
     </row>
     <row r="26">
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0.643643059036058</v>
+        <v>0.6436430589688942</v>
       </c>
       <c r="D26">
-        <v>0.6607478569503746</v>
+        <v>0.6607478568038931</v>
       </c>
       <c r="E26">
-        <v>0.6824024175880773</v>
+        <v>0.6824024171685525</v>
       </c>
       <c r="F26">
-        <v>0.694668234845035</v>
+        <v>0.6946682342648626</v>
       </c>
       <c r="G26">
-        <v>0.7038283457352166</v>
+        <v>0.7038283446462205</v>
       </c>
       <c r="H26">
-        <v>0.7157744390010624</v>
+        <v>0.7157744376775026</v>
       </c>
       <c r="I26">
-        <v>0.7374059753172015</v>
+        <v>0.7374059752211362</v>
       </c>
       <c r="J26">
-        <v>0.7857617118363971</v>
+        <v>0.7857617180714711</v>
       </c>
       <c r="K26">
-        <v>0.8241709802787103</v>
+        <v>0.8241709980820863</v>
       </c>
       <c r="L26">
-        <v>0.8492042828109301</v>
+        <v>0.8492043070156939</v>
       </c>
       <c r="M26">
-        <v>0.8771257292440526</v>
+        <v>0.8771257583357863</v>
       </c>
       <c r="N26">
-        <v>0.8953398359376862</v>
+        <v>0.8953398626245881</v>
       </c>
       <c r="O26">
-        <v>0.9094359937522729</v>
+        <v>0.9094360180637688</v>
       </c>
       <c r="P26">
-        <v>0.9196243994109886</v>
+        <v>0.9196244175768796</v>
       </c>
       <c r="Q26">
-        <v>0.9333125664937219</v>
+        <v>0.9333125771748735</v>
       </c>
     </row>
     <row r="27">
@@ -1826,49 +1826,49 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.6435691565508974</v>
+        <v>0.6435691564857373</v>
       </c>
       <c r="D27">
-        <v>0.6605499431309139</v>
+        <v>0.66054994298548</v>
       </c>
       <c r="E27">
-        <v>0.6812871811312768</v>
+        <v>0.6812871806842075</v>
       </c>
       <c r="F27">
-        <v>0.6925218906424037</v>
+        <v>0.6925218899901124</v>
       </c>
       <c r="G27">
-        <v>0.7000037964908183</v>
+        <v>0.7000037952319267</v>
       </c>
       <c r="H27">
-        <v>0.7074864729925403</v>
+        <v>0.7074864709844555</v>
       </c>
       <c r="I27">
-        <v>0.7167442989824901</v>
+        <v>0.7167442956178165</v>
       </c>
       <c r="J27">
-        <v>0.7392307037361072</v>
+        <v>0.7392306961070378</v>
       </c>
       <c r="K27">
-        <v>0.7585286140299142</v>
+        <v>0.758528607314942</v>
       </c>
       <c r="L27">
-        <v>0.7734864733688631</v>
+        <v>0.7734864690698751</v>
       </c>
       <c r="M27">
-        <v>0.7816578468911607</v>
+        <v>0.7816578444698501</v>
       </c>
       <c r="N27">
-        <v>0.7967872486406814</v>
+        <v>0.7967872524569435</v>
       </c>
       <c r="O27">
-        <v>0.8089131261226953</v>
+        <v>0.8089131361839709</v>
       </c>
       <c r="P27">
-        <v>0.8116973613255045</v>
+        <v>0.8116973679106421</v>
       </c>
       <c r="Q27">
-        <v>0.8267956429844036</v>
+        <v>0.8267956478217933</v>
       </c>
     </row>
     <row r="28">
@@ -1881,49 +1881,49 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0.6179891865896963</v>
+        <v>0.6179891866015162</v>
       </c>
       <c r="D28">
-        <v>0.6611152238378326</v>
+        <v>0.6611152237713082</v>
       </c>
       <c r="E28">
-        <v>0.6836626028756381</v>
+        <v>0.6836626025598704</v>
       </c>
       <c r="F28">
-        <v>0.6887345541958698</v>
+        <v>0.6887345538872895</v>
       </c>
       <c r="G28">
-        <v>0.6960480111656706</v>
+        <v>0.6960480103266826</v>
       </c>
       <c r="H28">
-        <v>0.7062118776724273</v>
+        <v>0.7062118753990116</v>
       </c>
       <c r="I28">
-        <v>0.709713034817502</v>
+        <v>0.7097130320335933</v>
       </c>
       <c r="J28">
-        <v>0.7363622836172203</v>
+        <v>0.7363622777038785</v>
       </c>
       <c r="K28">
-        <v>0.7427841844724516</v>
+        <v>0.7427841779928873</v>
       </c>
       <c r="L28">
-        <v>0.757822860353172</v>
+        <v>0.7578228559464546</v>
       </c>
       <c r="M28">
-        <v>0.7662494642028771</v>
+        <v>0.7662494584347559</v>
       </c>
       <c r="N28">
-        <v>0.7767167953365317</v>
+        <v>0.77671679294007</v>
       </c>
       <c r="O28">
-        <v>0.7866994273157979</v>
+        <v>0.7866994311490485</v>
       </c>
       <c r="P28">
-        <v>0.7921250303626941</v>
+        <v>0.7921250372877984</v>
       </c>
       <c r="Q28">
-        <v>0.8076328324146124</v>
+        <v>0.8076328427359666</v>
       </c>
     </row>
     <row r="29">
@@ -1936,49 +1936,49 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>0.6178848867318328</v>
+        <v>0.6178848867457871</v>
       </c>
       <c r="D29">
-        <v>0.6610786094462839</v>
+        <v>0.6610786093847789</v>
       </c>
       <c r="E29">
-        <v>0.6834860611700893</v>
+        <v>0.6834860608602404</v>
       </c>
       <c r="F29">
-        <v>0.6885893400912492</v>
+        <v>0.6885893397904805</v>
       </c>
       <c r="G29">
-        <v>0.695833622446561</v>
+        <v>0.695833621633885</v>
       </c>
       <c r="H29">
-        <v>0.7055925712205507</v>
+        <v>0.7055925690327332</v>
       </c>
       <c r="I29">
-        <v>0.7089411430829455</v>
+        <v>0.7089411404110958</v>
       </c>
       <c r="J29">
-        <v>0.7349364769389461</v>
+        <v>0.7349364709209951</v>
       </c>
       <c r="K29">
-        <v>0.7415074642921033</v>
+        <v>0.7415074575521712</v>
       </c>
       <c r="L29">
-        <v>0.7568542498303981</v>
+        <v>0.7568542448442196</v>
       </c>
       <c r="M29">
-        <v>0.7649157545725253</v>
+        <v>0.7649157480563085</v>
       </c>
       <c r="N29">
-        <v>0.7749173248090728</v>
+        <v>0.7749173208381277</v>
       </c>
       <c r="O29">
-        <v>0.7835198925039324</v>
+        <v>0.7835198932301287</v>
       </c>
       <c r="P29">
-        <v>0.7882716410613257</v>
+        <v>0.788271644260203</v>
       </c>
       <c r="Q29">
-        <v>0.8009491368097972</v>
+        <v>0.8009491441325753</v>
       </c>
     </row>
     <row r="30">
@@ -1991,49 +1991,49 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.6178146309984232</v>
+        <v>0.6178146310136537</v>
       </c>
       <c r="D30">
-        <v>0.6610574173285608</v>
+        <v>0.6610574172698331</v>
       </c>
       <c r="E30">
-        <v>0.6833779493554066</v>
+        <v>0.6833779490519853</v>
       </c>
       <c r="F30">
-        <v>0.6885050392337422</v>
+        <v>0.6885050389420853</v>
       </c>
       <c r="G30">
-        <v>0.6957169276824462</v>
+        <v>0.6957169268955381</v>
       </c>
       <c r="H30">
-        <v>0.7052657659617585</v>
+        <v>0.7052657638497026</v>
       </c>
       <c r="I30">
-        <v>0.708541238120582</v>
+        <v>0.7085412355449253</v>
       </c>
       <c r="J30">
-        <v>0.7341999190195752</v>
+        <v>0.7341999130270795</v>
       </c>
       <c r="K30">
-        <v>0.7408773663386967</v>
+        <v>0.7408773595551421</v>
       </c>
       <c r="L30">
-        <v>0.7565936723959916</v>
+        <v>0.7565936672841623</v>
       </c>
       <c r="M30">
-        <v>0.7646208076536372</v>
+        <v>0.7646208010122885</v>
       </c>
       <c r="N30">
-        <v>0.7744324548962728</v>
+        <v>0.774432450510616</v>
       </c>
       <c r="O30">
-        <v>0.7826804810354266</v>
+        <v>0.7826804807662116</v>
       </c>
       <c r="P30">
-        <v>0.7873159526512181</v>
+        <v>0.7873159546265008</v>
       </c>
       <c r="Q30">
-        <v>0.7980438149125544</v>
+        <v>0.7980438206644715</v>
       </c>
     </row>
     <row r="31">
@@ -2046,49 +2046,49 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0.6176325889485793</v>
+        <v>0.6176325889673548</v>
       </c>
       <c r="D31">
-        <v>0.6609981323144348</v>
+        <v>0.6609981322631662</v>
       </c>
       <c r="E31">
-        <v>0.6831351137334064</v>
+        <v>0.6831351134499069</v>
       </c>
       <c r="F31">
-        <v>0.6883233221319154</v>
+        <v>0.6883233218668205</v>
       </c>
       <c r="G31">
-        <v>0.6954741708434762</v>
+        <v>0.6954741701198959</v>
       </c>
       <c r="H31">
-        <v>0.7044678160203042</v>
+        <v>0.704467814096515</v>
       </c>
       <c r="I31">
-        <v>0.707510463727157</v>
+        <v>0.7075104613992718</v>
       </c>
       <c r="J31">
-        <v>0.7315454497338227</v>
+        <v>0.7315454439490272</v>
       </c>
       <c r="K31">
-        <v>0.7382764610092023</v>
+        <v>0.7382764542401323</v>
       </c>
       <c r="L31">
-        <v>0.7541596523540838</v>
+        <v>0.7541596466828143</v>
       </c>
       <c r="M31">
-        <v>0.7622905377148462</v>
+        <v>0.7622905305611709</v>
       </c>
       <c r="N31">
-        <v>0.7709882594654982</v>
+        <v>0.7709882537035537</v>
       </c>
       <c r="O31">
-        <v>0.7778701055902639</v>
+        <v>0.7778701026809433</v>
       </c>
       <c r="P31">
-        <v>0.7818142748581243</v>
+        <v>0.7818142738135706</v>
       </c>
       <c r="Q31">
-        <v>0.7889477468538194</v>
+        <v>0.7889477493910303</v>
       </c>
     </row>
     <row r="32">
@@ -2101,49 +2101,49 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0.6180798884888821</v>
+        <v>0.6180798884993984</v>
       </c>
       <c r="D32">
-        <v>0.661174442282767</v>
+        <v>0.661174442213132</v>
       </c>
       <c r="E32">
-        <v>0.6838510955361977</v>
+        <v>0.6838510952217719</v>
       </c>
       <c r="F32">
-        <v>0.6889228491124338</v>
+        <v>0.688922848802207</v>
       </c>
       <c r="G32">
-        <v>0.6964035925163539</v>
+        <v>0.6964035916512616</v>
       </c>
       <c r="H32">
-        <v>0.7077767500089767</v>
+        <v>0.7077767476584839</v>
       </c>
       <c r="I32">
-        <v>0.7118187606643449</v>
+        <v>0.7118187578119486</v>
       </c>
       <c r="J32">
-        <v>0.7431808669189185</v>
+        <v>0.7431808619736284</v>
       </c>
       <c r="K32">
-        <v>0.7503701524050619</v>
+        <v>0.7503701474690325</v>
       </c>
       <c r="L32">
-        <v>0.7673365562319682</v>
+        <v>0.7673365552339745</v>
       </c>
       <c r="M32">
-        <v>0.7781592678344087</v>
+        <v>0.7781592663634087</v>
       </c>
       <c r="N32">
-        <v>0.7945010048580714</v>
+        <v>0.7945010106176846</v>
       </c>
       <c r="O32">
-        <v>0.8112410023459448</v>
+        <v>0.811241017376892</v>
       </c>
       <c r="P32">
-        <v>0.817506386068773</v>
+        <v>0.8175064035131481</v>
       </c>
       <c r="Q32">
-        <v>0.8312356677261645</v>
+        <v>0.8312356895993132</v>
       </c>
     </row>
     <row r="33">
@@ -2156,49 +2156,49 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.6180592335406229</v>
+        <v>0.6180592335517461</v>
       </c>
       <c r="D33">
-        <v>0.66116444829425</v>
+        <v>0.6611644482259755</v>
       </c>
       <c r="E33">
-        <v>0.6838012519195112</v>
+        <v>0.6838012516077212</v>
       </c>
       <c r="F33">
-        <v>0.6888709840074104</v>
+        <v>0.6888709837025475</v>
       </c>
       <c r="G33">
-        <v>0.6963204791949642</v>
+        <v>0.6963204783503028</v>
       </c>
       <c r="H33">
-        <v>0.7074913603255171</v>
+        <v>0.7074913580445941</v>
       </c>
       <c r="I33">
-        <v>0.7114491513952791</v>
+        <v>0.7114491486282617</v>
       </c>
       <c r="J33">
-        <v>0.7423612951787404</v>
+        <v>0.7423612902436345</v>
       </c>
       <c r="K33">
-        <v>0.7495453886269636</v>
+        <v>0.7495453836318582</v>
       </c>
       <c r="L33">
-        <v>0.7665749868376014</v>
+        <v>0.7665749856751454</v>
       </c>
       <c r="M33">
-        <v>0.7772216719199205</v>
+        <v>0.777221670128255</v>
       </c>
       <c r="N33">
-        <v>0.7937793159931373</v>
+        <v>0.7937793211123556</v>
       </c>
       <c r="O33">
-        <v>0.8104287431268917</v>
+        <v>0.8104287570867508</v>
       </c>
       <c r="P33">
-        <v>0.8167861382579822</v>
+        <v>0.8167861543881101</v>
       </c>
       <c r="Q33">
-        <v>0.8308019003483891</v>
+        <v>0.8308019184351164</v>
       </c>
     </row>
     <row r="34">
@@ -2211,49 +2211,49 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0.6180310735987883</v>
+        <v>0.6180310736105222</v>
       </c>
       <c r="D34">
-        <v>0.6611521097597738</v>
+        <v>0.6611521096925692</v>
       </c>
       <c r="E34">
-        <v>0.6837308856743245</v>
+        <v>0.6837308853640313</v>
       </c>
       <c r="F34">
-        <v>0.6888038109726343</v>
+        <v>0.6888038106701424</v>
       </c>
       <c r="G34">
-        <v>0.6962044028996262</v>
+        <v>0.6962044020648903</v>
       </c>
       <c r="H34">
-        <v>0.7070722927604218</v>
+        <v>0.7070722904940367</v>
       </c>
       <c r="I34">
-        <v>0.7108927045641135</v>
+        <v>0.7108927018031206</v>
       </c>
       <c r="J34">
-        <v>0.7408014526744857</v>
+        <v>0.7408014473509696</v>
       </c>
       <c r="K34">
-        <v>0.7477674868031832</v>
+        <v>0.7477674812294375</v>
       </c>
       <c r="L34">
-        <v>0.7637391426381358</v>
+        <v>0.7637391400866147</v>
       </c>
       <c r="M34">
-        <v>0.7734920332965789</v>
+        <v>0.7734920297714635</v>
       </c>
       <c r="N34">
-        <v>0.7884367946622814</v>
+        <v>0.7884367964762423</v>
       </c>
       <c r="O34">
-        <v>0.804048843885897</v>
+        <v>0.8040488537789454</v>
       </c>
       <c r="P34">
-        <v>0.8098402207905973</v>
+        <v>0.8098402325800589</v>
       </c>
       <c r="Q34">
-        <v>0.8236718459068502</v>
+        <v>0.8236718578523646</v>
       </c>
     </row>
     <row r="35">
@@ -2266,49 +2266,49 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0.617995194249328</v>
+        <v>0.617995194261569</v>
       </c>
       <c r="D35">
-        <v>0.6611417899323763</v>
+        <v>0.6611417898659965</v>
       </c>
       <c r="E35">
-        <v>0.6836410818050516</v>
+        <v>0.6836410814938477</v>
       </c>
       <c r="F35">
-        <v>0.6887230346077483</v>
+        <v>0.6887230343037238</v>
       </c>
       <c r="G35">
-        <v>0.6960749758000186</v>
+        <v>0.6960749749662334</v>
       </c>
       <c r="H35">
-        <v>0.7066742281563816</v>
+        <v>0.7066742258667384</v>
       </c>
       <c r="I35">
-        <v>0.7103690221384849</v>
+        <v>0.7103690193349264</v>
       </c>
       <c r="J35">
-        <v>0.7394452486860534</v>
+        <v>0.7394452428240018</v>
       </c>
       <c r="K35">
-        <v>0.7462042379762602</v>
+        <v>0.7462042316341396</v>
       </c>
       <c r="L35">
-        <v>0.7612108448963886</v>
+        <v>0.7612108406507569</v>
       </c>
       <c r="M35">
-        <v>0.770039119328475</v>
+        <v>0.7700391136141292</v>
       </c>
       <c r="N35">
-        <v>0.7832830265259871</v>
+        <v>0.7832830241647174</v>
       </c>
       <c r="O35">
-        <v>0.7965826135905658</v>
+        <v>0.7965826171981045</v>
       </c>
       <c r="P35">
-        <v>0.8013718017417313</v>
+        <v>0.8013718066835418</v>
       </c>
       <c r="Q35">
-        <v>0.8119303040251304</v>
+        <v>0.8119303080145418</v>
       </c>
     </row>
     <row r="36">
@@ -2321,49 +2321,49 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.6176374428783138</v>
+        <v>0.6176374428955664</v>
       </c>
       <c r="D36">
-        <v>0.6610309869644317</v>
+        <v>0.6610309869122564</v>
       </c>
       <c r="E36">
-        <v>0.6830410955684432</v>
+        <v>0.6830410952847965</v>
       </c>
       <c r="F36">
-        <v>0.6882641874686758</v>
+        <v>0.688264187204386</v>
       </c>
       <c r="G36">
-        <v>0.6954382226243554</v>
+        <v>0.6954382219054712</v>
       </c>
       <c r="H36">
-        <v>0.704601317694082</v>
+        <v>0.7046013157798527</v>
       </c>
       <c r="I36">
-        <v>0.7076719493595529</v>
+        <v>0.7076719470447799</v>
       </c>
       <c r="J36">
-        <v>0.7328392466161948</v>
+        <v>0.7328392408816321</v>
       </c>
       <c r="K36">
-        <v>0.7398914845152426</v>
+        <v>0.7398914778506011</v>
       </c>
       <c r="L36">
-        <v>0.7553611808501715</v>
+        <v>0.7553611753547694</v>
       </c>
       <c r="M36">
-        <v>0.7629851017662035</v>
+        <v>0.7629850947860841</v>
       </c>
       <c r="N36">
-        <v>0.7734014676482637</v>
+        <v>0.7734014622366525</v>
       </c>
       <c r="O36">
-        <v>0.7810384565266301</v>
+        <v>0.7810384542294808</v>
       </c>
       <c r="P36">
-        <v>0.784842566190218</v>
+        <v>0.7848425654260541</v>
       </c>
       <c r="Q36">
-        <v>0.7916868678540425</v>
+        <v>0.7916868690815128</v>
       </c>
     </row>
     <row r="37">
@@ -2376,49 +2376,49 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0.6491293981171593</v>
+        <v>0.6491293974836646</v>
       </c>
       <c r="D37">
-        <v>0.6726938100643867</v>
+        <v>0.6726938094357966</v>
       </c>
       <c r="E37">
-        <v>0.7138724559852694</v>
+        <v>0.713872453569791</v>
       </c>
       <c r="F37">
-        <v>0.7330735681796979</v>
+        <v>0.7330735650141639</v>
       </c>
       <c r="G37">
-        <v>0.7641145701796569</v>
+        <v>0.7641145729134087</v>
       </c>
       <c r="H37">
-        <v>0.8050135970665708</v>
+        <v>0.8050136128397272</v>
       </c>
       <c r="I37">
-        <v>0.8312799512450997</v>
+        <v>0.8312799815672782</v>
       </c>
       <c r="J37">
-        <v>0.844798996076043</v>
+        <v>0.8447990342058093</v>
       </c>
       <c r="K37">
-        <v>0.8552680924950157</v>
+        <v>0.855268129262565</v>
       </c>
       <c r="L37">
-        <v>0.867386202617997</v>
+        <v>0.8673862380756263</v>
       </c>
       <c r="M37">
-        <v>0.8786659602863093</v>
+        <v>0.8786659982071164</v>
       </c>
       <c r="N37">
-        <v>0.8873752875208518</v>
+        <v>0.887375330747286</v>
       </c>
       <c r="O37">
-        <v>0.9006802935262573</v>
+        <v>0.9006803613184917</v>
       </c>
       <c r="P37">
-        <v>0.9084155037317208</v>
+        <v>0.9084155839464005</v>
       </c>
       <c r="Q37">
-        <v>0.9158862420280217</v>
+        <v>0.9158863365929928</v>
       </c>
     </row>
     <row r="38">
@@ -2431,49 +2431,49 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0.6472802226904981</v>
+        <v>0.6472802219905976</v>
       </c>
       <c r="D38">
-        <v>0.6663741688953713</v>
+        <v>0.6663741680455113</v>
       </c>
       <c r="E38">
-        <v>0.697702230969182</v>
+        <v>0.6977022290907371</v>
       </c>
       <c r="F38">
-        <v>0.7109358571589171</v>
+        <v>0.7109358538318201</v>
       </c>
       <c r="G38">
-        <v>0.723360917531636</v>
+        <v>0.7233609125605374</v>
       </c>
       <c r="H38">
-        <v>0.7396261355081913</v>
+        <v>0.7396261330782155</v>
       </c>
       <c r="I38">
-        <v>0.7539983296425135</v>
+        <v>0.753998330398027</v>
       </c>
       <c r="J38">
-        <v>0.7792358700064386</v>
+        <v>0.7792358752792456</v>
       </c>
       <c r="K38">
-        <v>0.7947521245689063</v>
+        <v>0.7947521338282755</v>
       </c>
       <c r="L38">
-        <v>0.8287249317479332</v>
+        <v>0.8287249604958051</v>
       </c>
       <c r="M38">
-        <v>0.849121666411473</v>
+        <v>0.8491216692996308</v>
       </c>
       <c r="N38">
-        <v>0.8530308527280686</v>
+        <v>0.8530308856965728</v>
       </c>
       <c r="O38">
-        <v>0.8677731712103081</v>
+        <v>0.867773223578244</v>
       </c>
       <c r="P38">
-        <v>0.8766867149564259</v>
+        <v>0.8766867646095983</v>
       </c>
       <c r="Q38">
-        <v>0.8833651244186799</v>
+        <v>0.8833651731229223</v>
       </c>
     </row>
     <row r="39">
@@ -2486,49 +2486,49 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0.6472287373179957</v>
+        <v>0.647228736624641</v>
       </c>
       <c r="D39">
-        <v>0.6662561930641608</v>
+        <v>0.6662561921609627</v>
       </c>
       <c r="E39">
-        <v>0.6951197036800285</v>
+        <v>0.6951197017243294</v>
       </c>
       <c r="F39">
-        <v>0.7082661397085106</v>
+        <v>0.7082661357708864</v>
       </c>
       <c r="G39">
-        <v>0.7204592489087327</v>
+        <v>0.7204592425498192</v>
       </c>
       <c r="H39">
-        <v>0.7364241948925039</v>
+        <v>0.7364241889241603</v>
       </c>
       <c r="I39">
-        <v>0.7469732062341955</v>
+        <v>0.7469732010820553</v>
       </c>
       <c r="J39">
-        <v>0.7646449185916887</v>
+        <v>0.7646449146027694</v>
       </c>
       <c r="K39">
-        <v>0.7802541028556874</v>
+        <v>0.7802540994664462</v>
       </c>
       <c r="L39">
-        <v>0.8000112483524892</v>
+        <v>0.8000112465597109</v>
       </c>
       <c r="M39">
-        <v>0.80700683213346</v>
+        <v>0.807006829395282</v>
       </c>
       <c r="N39">
-        <v>0.827274343004009</v>
+        <v>0.827274351789443</v>
       </c>
       <c r="O39">
-        <v>0.8401025460734068</v>
+        <v>0.8401025601720132</v>
       </c>
       <c r="P39">
-        <v>0.848624980571242</v>
+        <v>0.8486249966415282</v>
       </c>
       <c r="Q39">
-        <v>0.8612558416679517</v>
+        <v>0.8612558788575371</v>
       </c>
     </row>
     <row r="40">
@@ -2541,49 +2541,49 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0.619735203434455</v>
+        <v>0.6197352015763288</v>
       </c>
       <c r="D40">
-        <v>0.6333832928066546</v>
+        <v>0.6333832920684528</v>
       </c>
       <c r="E40">
-        <v>0.6787383133515561</v>
+        <v>0.6787383138212542</v>
       </c>
       <c r="F40">
-        <v>0.7124562340646758</v>
+        <v>0.7124562328143054</v>
       </c>
       <c r="G40">
-        <v>0.7496361943136062</v>
+        <v>0.7496362009720235</v>
       </c>
       <c r="H40">
-        <v>0.7695284008053538</v>
+        <v>0.7695284086164346</v>
       </c>
       <c r="I40">
-        <v>0.7976390916157918</v>
+        <v>0.7976391115670192</v>
       </c>
       <c r="J40">
-        <v>0.8204771615311517</v>
+        <v>0.8204771921701448</v>
       </c>
       <c r="K40">
-        <v>0.8370226248867162</v>
+        <v>0.8370226563979093</v>
       </c>
       <c r="L40">
-        <v>0.848164293111459</v>
+        <v>0.8481643268437629</v>
       </c>
       <c r="M40">
-        <v>0.8611226525745019</v>
+        <v>0.8611226841895985</v>
       </c>
       <c r="N40">
-        <v>0.874107463704207</v>
+        <v>0.874107506403637</v>
       </c>
       <c r="O40">
-        <v>0.8878957158863929</v>
+        <v>0.8878957750936631</v>
       </c>
       <c r="P40">
-        <v>0.8982594701310169</v>
+        <v>0.898259526472314</v>
       </c>
       <c r="Q40">
-        <v>0.9086657345150582</v>
+        <v>0.9086657915635197</v>
       </c>
     </row>
     <row r="41">
@@ -2596,49 +2596,49 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.6173773223053315</v>
+        <v>0.6173773222893426</v>
       </c>
       <c r="D41">
-        <v>0.6628752012978114</v>
+        <v>0.6628752020505418</v>
       </c>
       <c r="E41">
-        <v>0.7229838463206135</v>
+        <v>0.7229838493183236</v>
       </c>
       <c r="F41">
-        <v>0.7601420134698175</v>
+        <v>0.760142017794564</v>
       </c>
       <c r="G41">
-        <v>0.7912858450045748</v>
+        <v>0.7912858532086549</v>
       </c>
       <c r="H41">
-        <v>0.8183358407599028</v>
+        <v>0.8183358537432327</v>
       </c>
       <c r="I41">
-        <v>0.8360150271944462</v>
+        <v>0.8360150394881654</v>
       </c>
       <c r="J41">
-        <v>0.8472208098695676</v>
+        <v>0.8472208224127464</v>
       </c>
       <c r="K41">
-        <v>0.8625139580719926</v>
+        <v>0.8625139736760895</v>
       </c>
       <c r="L41">
-        <v>0.8700905091512906</v>
+        <v>0.8700905259785945</v>
       </c>
       <c r="M41">
-        <v>0.888471474998785</v>
+        <v>0.8884714914446397</v>
       </c>
       <c r="N41">
-        <v>0.9070302450830061</v>
+        <v>0.9070302617557144</v>
       </c>
       <c r="O41">
-        <v>0.9182267021434549</v>
+        <v>0.9182267183582721</v>
       </c>
       <c r="P41">
-        <v>0.9278150153230389</v>
+        <v>0.9278150284209226</v>
       </c>
       <c r="Q41">
-        <v>0.9365466625774925</v>
+        <v>0.9365466735039305</v>
       </c>
     </row>
     <row r="42">
@@ -2651,49 +2651,49 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.5038544743145424</v>
+        <v>0.503854469106769</v>
       </c>
       <c r="D42">
-        <v>0.6511762017213585</v>
+        <v>0.6511762012683223</v>
       </c>
       <c r="E42">
-        <v>0.6744938819741688</v>
+        <v>0.6744938813866904</v>
       </c>
       <c r="F42">
-        <v>0.7216140036739931</v>
+        <v>0.7216139995210047</v>
       </c>
       <c r="G42">
-        <v>0.751146005814281</v>
+        <v>0.7511460017569795</v>
       </c>
       <c r="H42">
-        <v>0.7658088206510554</v>
+        <v>0.7658088152039755</v>
       </c>
       <c r="I42">
-        <v>0.7826458849980422</v>
+        <v>0.7826458789567519</v>
       </c>
       <c r="J42">
-        <v>0.7947978155069327</v>
+        <v>0.7947978048339628</v>
       </c>
       <c r="K42">
-        <v>0.8287876589326277</v>
+        <v>0.8287876457515237</v>
       </c>
       <c r="L42">
-        <v>0.8484811224511225</v>
+        <v>0.8484811094726428</v>
       </c>
       <c r="M42">
-        <v>0.864581405783565</v>
+        <v>0.8645813935470631</v>
       </c>
       <c r="N42">
-        <v>0.8933271136131946</v>
+        <v>0.8933271058954488</v>
       </c>
       <c r="O42">
-        <v>0.9007914603296567</v>
+        <v>0.900791452793072</v>
       </c>
       <c r="P42">
-        <v>0.9094671571744516</v>
+        <v>0.9094671460999927</v>
       </c>
       <c r="Q42">
-        <v>0.9226142305883073</v>
+        <v>0.9226142191523412</v>
       </c>
     </row>
     <row r="43">
@@ -2706,49 +2706,49 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>0.6355865009659161</v>
+        <v>0.6355865011206092</v>
       </c>
       <c r="D43">
-        <v>0.669414599609491</v>
+        <v>0.6694146000518137</v>
       </c>
       <c r="E43">
-        <v>0.7030182470801745</v>
+        <v>0.7030182470275347</v>
       </c>
       <c r="F43">
-        <v>0.7259403648356724</v>
+        <v>0.7259403644686389</v>
       </c>
       <c r="G43">
-        <v>0.7571791451578468</v>
+        <v>0.7571791454238677</v>
       </c>
       <c r="H43">
-        <v>0.7788414061450253</v>
+        <v>0.7788414077843024</v>
       </c>
       <c r="I43">
-        <v>0.8037869263306345</v>
+        <v>0.8037869288504806</v>
       </c>
       <c r="J43">
-        <v>0.8175071837806387</v>
+        <v>0.8175071863120069</v>
       </c>
       <c r="K43">
-        <v>0.8386567458185377</v>
+        <v>0.8386567468447788</v>
       </c>
       <c r="L43">
-        <v>0.8669944780684178</v>
+        <v>0.866994479100287</v>
       </c>
       <c r="M43">
-        <v>0.883769512092448</v>
+        <v>0.8837695154590711</v>
       </c>
       <c r="N43">
-        <v>0.8975871751366885</v>
+        <v>0.8975871820087352</v>
       </c>
       <c r="O43">
-        <v>0.9090488446200516</v>
+        <v>0.9090488525643271</v>
       </c>
       <c r="P43">
-        <v>0.9204252326123947</v>
+        <v>0.9204252433592552</v>
       </c>
       <c r="Q43">
-        <v>0.9274162461382027</v>
+        <v>0.9274162547352472</v>
       </c>
     </row>
   </sheetData>
